--- a/Seminar/Statistics_by_Python/atom_data.xlsx
+++ b/Seminar/Statistics_by_Python/atom_data.xlsx
@@ -10,12 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D0F6FC-56D3-4753-BD50-07C281A64DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
